--- a/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_39.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.3/Output_6_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2253719.236885474</v>
+        <v>2246786.835085625</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9630586.081252649</v>
+        <v>9630586.081252646</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9630586.081252649</v>
+        <v>9630586.081252646</v>
       </c>
     </row>
     <row r="9">
@@ -702,10 +702,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>28.70619138541469</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>123.5543591877376</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>341.9742620710304</v>
       </c>
       <c r="C3" t="n">
-        <v>341.9742620710307</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -845,7 +845,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
-        <v>119.040440756494</v>
+        <v>120.6316114025499</v>
       </c>
       <c r="N4" t="n">
         <v>171.1850752716849</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>326.6021279811511</v>
+        <v>325.0109573350953</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>3.75737228701621</v>
+        <v>32.46356367243068</v>
       </c>
       <c r="H5" t="n">
         <v>8.009658703527407</v>
@@ -945,7 +945,7 @@
         <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
-        <v>215.3817731139785</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>182.885439975089</v>
+        <v>199.8180013219744</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>336.7086723952407</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1252,19 +1252,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>240.5675466535028</v>
+        <v>147.2737972923793</v>
       </c>
       <c r="S9" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T9" t="n">
-        <v>385</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>385</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1368,7 +1368,7 @@
         <v>131.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>99.47457824299391</v>
+        <v>103.4399696284084</v>
       </c>
       <c r="D11" t="n">
         <v>60.33915573984979</v>
@@ -1422,7 +1422,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>303.1866879340253</v>
+        <v>299.2212965486107</v>
       </c>
       <c r="V11" t="n">
         <v>279.8510241668239</v>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>62.67776252544248</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S12" t="n">
         <v>116.5639999646113</v>
@@ -1501,7 +1501,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U12" t="n">
-        <v>112.8881222856292</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V12" t="n">
         <v>64.51066719152016</v>
@@ -1513,7 +1513,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y12" t="n">
-        <v>49.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1614,7 +1614,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F14" t="n">
-        <v>54.88962870801186</v>
+        <v>58.85502009342638</v>
       </c>
       <c r="G14" t="n">
         <v>53.75737228701621</v>
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C15" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>62.67776252544254</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T15" t="n">
-        <v>55.35776521751382</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U15" t="n">
         <v>50.21035976018675</v>
       </c>
       <c r="V15" t="n">
-        <v>64.51066719152016</v>
+        <v>127.1884297169626</v>
       </c>
       <c r="W15" t="n">
         <v>82.37314290982852</v>
@@ -1887,10 +1887,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S17" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T17" t="n">
         <v>236.6755817285639</v>
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>239.5984974349628</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1963,10 +1963,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>259.9515598178217</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S18" t="n">
         <v>116.5639999646113</v>
@@ -1975,7 +1975,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U18" t="n">
-        <v>400.2103597601867</v>
+        <v>50.21035976018675</v>
       </c>
       <c r="V18" t="n">
         <v>64.51066719152016</v>
@@ -2097,7 +2097,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>288.3734759809475</v>
       </c>
       <c r="X20" t="n">
-        <v>242.2818334606677</v>
+        <v>246.2472248460823</v>
       </c>
       <c r="Y20" t="n">
         <v>161.3174326828064</v>
@@ -2215,7 +2215,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V21" t="n">
-        <v>127.1884297169627</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W21" t="n">
         <v>82.37314290982852</v>
@@ -2224,7 +2224,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>49.39139276613435</v>
+        <v>112.0691552915768</v>
       </c>
     </row>
     <row r="22">
@@ -2331,7 +2331,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H23" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         <v>299.2212965486107</v>
       </c>
       <c r="V23" t="n">
-        <v>279.8510241668239</v>
+        <v>283.8164155522384</v>
       </c>
       <c r="W23" t="n">
         <v>288.3734759809475</v>
@@ -2398,13 +2398,13 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>62.67776252544248</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>142.9042596329532</v>
       </c>
       <c r="Y24" t="n">
         <v>49.39139276613435</v>
@@ -2738,22 +2738,22 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>121.5476281577792</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>269.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>338.445564079015</v>
+        <v>181.3918717271878</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>385.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>80.75675786254469</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>424.6021279811511</v>
@@ -2835,10 +2835,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>7.224591385414723</v>
       </c>
       <c r="S29" t="n">
-        <v>200.0727591877375</v>
+        <v>192.8481678023229</v>
       </c>
       <c r="T29" t="n">
         <v>284.6755817285639</v>
@@ -2978,25 +2978,25 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>80.75675786254469</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>269.1850752716849</v>
       </c>
       <c r="O31" t="n">
-        <v>338.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>385.4478973282775</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>424.6021279811511</v>
+        <v>397.9830728915778</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>60.37347970285543</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3072,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>7.224591385414723</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>192.8481678023229</v>
+        <v>200.0727591877375</v>
       </c>
       <c r="T32" t="n">
         <v>284.6755817285639</v>
@@ -3212,25 +3212,25 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>121.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>218.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>170.4644523845533</v>
       </c>
       <c r="O34" t="n">
-        <v>143.0005026298672</v>
+        <v>338.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>385.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>423.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>424.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T35" t="n">
         <v>236.6755817285639</v>
@@ -3400,13 +3400,13 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V36" t="n">
-        <v>64.51066719152016</v>
+        <v>134.5163324950501</v>
       </c>
       <c r="W36" t="n">
         <v>82.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>139.8684047489175</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>49.39139276613435</v>
@@ -3516,10 +3516,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H38" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>62.67776252544243</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3625,7 +3625,7 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>259.9515598178218</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S39" t="n">
         <v>116.5639999646113</v>
@@ -3640,7 +3640,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>82.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
         <v>69.86273944538755</v>
@@ -3747,7 +3747,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F41" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G41" t="n">
         <v>53.75737228701621</v>
@@ -3789,7 +3789,7 @@
         <v>144.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>236.6755817285639</v>
+        <v>240.6409731139784</v>
       </c>
       <c r="U41" t="n">
         <v>299.2212965486107</v>
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>195.551376634094</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>547.2737972923793</v>
+        <v>197.2737972923793</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3877,7 +3877,7 @@
         <v>64.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>145.0509054352709</v>
+        <v>82.37314290982852</v>
       </c>
       <c r="X42" t="n">
         <v>69.86273944538755</v>
@@ -3990,10 +3990,10 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H44" t="n">
-        <v>61.97505008894191</v>
+        <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4054,10 +4054,10 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>75.83998807325922</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V45" t="n">
-        <v>64.51066719152016</v>
+        <v>260.0620438256142</v>
       </c>
       <c r="W45" t="n">
         <v>82.37314290982852</v>
@@ -4321,16 +4321,16 @@
         <v>30.8</v>
       </c>
       <c r="J2" t="n">
-        <v>411.95</v>
+        <v>30.8</v>
       </c>
       <c r="K2" t="n">
-        <v>411.95</v>
+        <v>396.55</v>
       </c>
       <c r="L2" t="n">
-        <v>411.95</v>
+        <v>396.55</v>
       </c>
       <c r="M2" t="n">
-        <v>793.1</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="N2" t="n">
         <v>1158.85</v>
@@ -4345,7 +4345,7 @@
         <v>1540</v>
       </c>
       <c r="R2" t="n">
-        <v>1511.00384708544</v>
+        <v>1540</v>
       </c>
       <c r="S2" t="n">
         <v>1415.197616982083</v>
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>722.3619790837812</v>
+        <v>730.70101116875</v>
       </c>
       <c r="C3" t="n">
-        <v>376.9334315372855</v>
+        <v>730.70101116875</v>
       </c>
       <c r="D3" t="n">
-        <v>376.9334315372855</v>
+        <v>730.70101116875</v>
       </c>
       <c r="E3" t="n">
-        <v>30.8</v>
+        <v>384.5675796314646</v>
       </c>
       <c r="F3" t="n">
-        <v>30.8</v>
+        <v>384.5675796314646</v>
       </c>
       <c r="G3" t="n">
-        <v>30.8</v>
+        <v>384.5675796314646</v>
       </c>
       <c r="H3" t="n">
-        <v>30.8</v>
+        <v>384.5675796314646</v>
       </c>
       <c r="I3" t="n">
-        <v>30.8</v>
+        <v>384.5675796314646</v>
       </c>
       <c r="J3" t="n">
-        <v>154.756520175299</v>
+        <v>508.5240998067635</v>
       </c>
       <c r="K3" t="n">
-        <v>343.9493362696824</v>
+        <v>697.7169159011469</v>
       </c>
       <c r="L3" t="n">
-        <v>615.2997978648825</v>
+        <v>969.0673774963469</v>
       </c>
       <c r="M3" t="n">
-        <v>701.3803396077418</v>
+        <v>1055.147919239206</v>
       </c>
       <c r="N3" t="n">
-        <v>834.6606242153101</v>
+        <v>1188.428203846775</v>
       </c>
       <c r="O3" t="n">
-        <v>1073.703075899029</v>
+        <v>1427.470655530493</v>
       </c>
       <c r="P3" t="n">
-        <v>1186.232420368536</v>
+        <v>1540</v>
       </c>
       <c r="Q3" t="n">
-        <v>1011.404879873102</v>
+        <v>1365.172459504566</v>
       </c>
       <c r="R3" t="n">
-        <v>862.6434684666581</v>
+        <v>1216.411048098122</v>
       </c>
       <c r="S3" t="n">
-        <v>795.4071048660406</v>
+        <v>1149.174684497505</v>
       </c>
       <c r="T3" t="n">
-        <v>789.9952208079459</v>
+        <v>1143.76280043941</v>
       </c>
       <c r="U3" t="n">
-        <v>789.7827362016966</v>
+        <v>1143.550315833161</v>
       </c>
       <c r="V3" t="n">
-        <v>775.1254966143025</v>
+        <v>1128.893076245767</v>
       </c>
       <c r="W3" t="n">
-        <v>742.4253522609404</v>
+        <v>1096.192931892404</v>
       </c>
       <c r="X3" t="n">
-        <v>722.3619790837812</v>
+        <v>1076.129558715245</v>
       </c>
       <c r="Y3" t="n">
-        <v>722.3619790837812</v>
+        <v>1076.129558715245</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>701.4985197772105</v>
+        <v>476.1725855242326</v>
       </c>
       <c r="C4" t="n">
-        <v>827.5005255956463</v>
+        <v>602.1745913426684</v>
       </c>
       <c r="D4" t="n">
-        <v>940.8196697206464</v>
+        <v>715.4937354676684</v>
       </c>
       <c r="E4" t="n">
-        <v>940.8196697206464</v>
+        <v>833.3226396790815</v>
       </c>
       <c r="F4" t="n">
-        <v>1065.180642312582</v>
+        <v>957.683612271017</v>
       </c>
       <c r="G4" t="n">
-        <v>1065.180642312582</v>
+        <v>1111.090178157902</v>
       </c>
       <c r="H4" t="n">
-        <v>1234.69722747198</v>
+        <v>1111.090178157902</v>
       </c>
       <c r="I4" t="n">
-        <v>1455.830106408063</v>
+        <v>1332.223057093985</v>
       </c>
       <c r="J4" t="n">
         <v>1540</v>
@@ -4488,43 +4488,43 @@
         <v>1516.214517012344</v>
       </c>
       <c r="M4" t="n">
-        <v>1395.97164756134</v>
+        <v>1394.364404484516</v>
       </c>
       <c r="N4" t="n">
-        <v>1223.057430115194</v>
+        <v>1221.450187038369</v>
       </c>
       <c r="O4" t="n">
-        <v>980.1831229646734</v>
+        <v>978.5758798878493</v>
       </c>
       <c r="P4" t="n">
-        <v>689.8317115219688</v>
+        <v>688.2244684451448</v>
       </c>
       <c r="Q4" t="n">
-        <v>360.7011393749001</v>
+        <v>359.0938962980761</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
       </c>
       <c r="S4" t="n">
-        <v>68.05025509417312</v>
+        <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>256.125934252978</v>
+        <v>30.8</v>
       </c>
       <c r="U4" t="n">
-        <v>502.6771268912646</v>
+        <v>277.3511926382866</v>
       </c>
       <c r="V4" t="n">
-        <v>701.4985197772105</v>
+        <v>476.1725855242326</v>
       </c>
       <c r="W4" t="n">
-        <v>701.4985197772105</v>
+        <v>476.1725855242326</v>
       </c>
       <c r="X4" t="n">
-        <v>701.4985197772105</v>
+        <v>476.1725855242326</v>
       </c>
       <c r="Y4" t="n">
-        <v>701.4985197772105</v>
+        <v>476.1725855242326</v>
       </c>
     </row>
     <row r="5">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C5" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D5" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E5" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F5" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G5" t="n">
         <v>38.89056434699738</v>
@@ -4561,22 +4561,22 @@
         <v>411.95</v>
       </c>
       <c r="K5" t="n">
-        <v>793.0999999999999</v>
+        <v>411.95</v>
       </c>
       <c r="L5" t="n">
-        <v>1174.25</v>
+        <v>411.95</v>
       </c>
       <c r="M5" t="n">
-        <v>1540</v>
+        <v>777.6999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="P5" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="Q5" t="n">
         <v>1540</v>
@@ -4588,22 +4588,22 @@
         <v>1444.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U5" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V5" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W5" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X5" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="6">
@@ -4619,13 +4619,13 @@
         <v>897.189519579215</v>
       </c>
       <c r="D6" t="n">
-        <v>712.45675192761</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="E6" t="n">
-        <v>366.3233203903244</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="F6" t="n">
-        <v>366.3233203903244</v>
+        <v>695.3531546075237</v>
       </c>
       <c r="G6" t="n">
         <v>366.3233203903244</v>
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>937.3561738414276</v>
+        <v>630.3233636224959</v>
       </c>
       <c r="C7" t="n">
-        <v>1063.358179659863</v>
+        <v>630.3233636224959</v>
       </c>
       <c r="D7" t="n">
-        <v>1176.677323784863</v>
+        <v>743.642507747496</v>
       </c>
       <c r="E7" t="n">
-        <v>1176.677323784863</v>
+        <v>861.471411958909</v>
       </c>
       <c r="F7" t="n">
-        <v>1260.118980903734</v>
+        <v>861.471411958909</v>
       </c>
       <c r="G7" t="n">
-        <v>1260.118980903734</v>
+        <v>957.7833804114658</v>
       </c>
       <c r="H7" t="n">
-        <v>1429.635566063132</v>
+        <v>957.7833804114658</v>
       </c>
       <c r="I7" t="n">
-        <v>1429.635566063132</v>
+        <v>1178.916259347549</v>
       </c>
       <c r="J7" t="n">
-        <v>1429.635566063132</v>
+        <v>1540</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
@@ -4749,19 +4749,19 @@
         <v>256.125934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>502.6771268912646</v>
+        <v>256.125934252978</v>
       </c>
       <c r="V7" t="n">
-        <v>502.6771268912646</v>
+        <v>256.125934252978</v>
       </c>
       <c r="W7" t="n">
-        <v>674.568045150942</v>
+        <v>256.125934252978</v>
       </c>
       <c r="X7" t="n">
-        <v>825.5988361751355</v>
+        <v>407.1567252771715</v>
       </c>
       <c r="Y7" t="n">
-        <v>825.5988361751355</v>
+        <v>518.5660259562038</v>
       </c>
     </row>
     <row r="8">
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.8</v>
+        <v>382.2522089875785</v>
       </c>
       <c r="C9" t="n">
-        <v>30.8</v>
+        <v>382.2522089875785</v>
       </c>
       <c r="D9" t="n">
         <v>30.8</v>
@@ -4895,31 +4895,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1186.232420368536</v>
+        <v>1011.404879873102</v>
       </c>
       <c r="R9" t="n">
-        <v>943.2348984963106</v>
+        <v>862.6434684666581</v>
       </c>
       <c r="S9" t="n">
-        <v>875.9985348956932</v>
+        <v>795.4071048660406</v>
       </c>
       <c r="T9" t="n">
-        <v>487.1096460068043</v>
+        <v>789.9952208079459</v>
       </c>
       <c r="U9" t="n">
-        <v>98.22075711791538</v>
+        <v>789.7827362016966</v>
       </c>
       <c r="V9" t="n">
-        <v>83.56351753052128</v>
+        <v>775.1254966143025</v>
       </c>
       <c r="W9" t="n">
-        <v>50.86337317715914</v>
+        <v>742.4253522609404</v>
       </c>
       <c r="X9" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
       <c r="Y9" t="n">
-        <v>30.8</v>
+        <v>722.3619790837812</v>
       </c>
     </row>
     <row r="10">
@@ -4929,25 +4929,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>625.2013882700642</v>
+        <v>947.7538505813088</v>
       </c>
       <c r="C10" t="n">
-        <v>751.2033940885</v>
+        <v>1073.755856399745</v>
       </c>
       <c r="D10" t="n">
-        <v>864.5225382135001</v>
+        <v>1187.075000524745</v>
       </c>
       <c r="E10" t="n">
-        <v>982.3514424249131</v>
+        <v>1187.075000524745</v>
       </c>
       <c r="F10" t="n">
-        <v>1106.712415016849</v>
+        <v>1187.075000524745</v>
       </c>
       <c r="G10" t="n">
-        <v>1260.118980903734</v>
+        <v>1208.502687127049</v>
       </c>
       <c r="H10" t="n">
-        <v>1429.635566063132</v>
+        <v>1208.502687127049</v>
       </c>
       <c r="I10" t="n">
         <v>1429.635566063132</v>
@@ -4980,25 +4980,25 @@
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="U10" t="n">
-        <v>277.3511926382866</v>
+        <v>314.6014477324597</v>
       </c>
       <c r="V10" t="n">
-        <v>302.2796789861933</v>
+        <v>513.4228406184056</v>
       </c>
       <c r="W10" t="n">
-        <v>474.1705972458707</v>
+        <v>685.313758878083</v>
       </c>
       <c r="X10" t="n">
-        <v>625.2013882700642</v>
+        <v>836.3445499022765</v>
       </c>
       <c r="Y10" t="n">
-        <v>625.2013882700642</v>
+        <v>947.7538505813088</v>
       </c>
     </row>
     <row r="11">
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C11" t="n">
         <v>328.9211162073474</v>
@@ -5032,22 +5032,22 @@
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K11" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L11" t="n">
-        <v>690.5809049473327</v>
+        <v>1151.54</v>
       </c>
       <c r="M11" t="n">
-        <v>690.5809049473327</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N11" t="n">
-        <v>690.5809049473327</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="O11" t="n">
-        <v>1243.990904947333</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="P11" t="n">
         <v>1797.400904947332</v>
@@ -5065,19 +5065,19 @@
         <v>1850.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X11" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y11" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="12">
@@ -5087,13 +5087,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C12" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D12" t="n">
-        <v>44.72</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="E12" t="n">
         <v>44.72</v>
@@ -5135,28 +5135,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R12" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S12" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T12" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U12" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V12" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W12" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X12" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y12" t="n">
-        <v>90.8376455473191</v>
+        <v>154.1485167851398</v>
       </c>
     </row>
     <row r="13">
@@ -5257,22 +5257,22 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G14" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H14" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K14" t="n">
-        <v>733.1420762183976</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="L14" t="n">
         <v>733.1420762183976</v>
@@ -5324,16 +5324,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
-        <v>108.0308712378207</v>
+        <v>44.72</v>
       </c>
       <c r="F15" t="n">
         <v>44.72</v>
@@ -5378,22 +5378,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T15" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>422.9747211415747</v>
       </c>
       <c r="V15" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X15" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y15" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5509,28 +5509,28 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>989.4391130376558</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>1542.849113037656</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M17" t="n">
-        <v>1542.849113037656</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N17" t="n">
-        <v>1542.849113037656</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O17" t="n">
-        <v>2096.259113037656</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P17" t="n">
-        <v>2096.259113037656</v>
+        <v>2236</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
       </c>
       <c r="R17" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S17" t="n">
         <v>2085.68327354774</v>
@@ -5561,19 +5561,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.93203277325181</v>
+        <v>297.950717050992</v>
       </c>
       <c r="C18" t="n">
-        <v>44.72</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="D18" t="n">
-        <v>44.72</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="E18" t="n">
-        <v>44.72</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="F18" t="n">
-        <v>44.72</v>
+        <v>286.7386842777402</v>
       </c>
       <c r="G18" t="n">
         <v>44.72</v>
@@ -5606,31 +5606,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R18" t="n">
-        <v>937.5750872192207</v>
+        <v>826.0584179616072</v>
       </c>
       <c r="S18" t="n">
-        <v>819.8336731135527</v>
+        <v>708.3170038559392</v>
       </c>
       <c r="T18" t="n">
-        <v>763.9167385504074</v>
+        <v>652.400069292794</v>
       </c>
       <c r="U18" t="n">
-        <v>359.6638499037541</v>
+        <v>601.6825341814942</v>
       </c>
       <c r="V18" t="n">
-        <v>294.5015598113094</v>
+        <v>536.5202440890496</v>
       </c>
       <c r="W18" t="n">
-        <v>211.2963649528968</v>
+        <v>453.3150492306369</v>
       </c>
       <c r="X18" t="n">
-        <v>140.7279412706871</v>
+        <v>382.7466255484273</v>
       </c>
       <c r="Y18" t="n">
-        <v>90.8376455473191</v>
+        <v>332.8563298250593</v>
       </c>
     </row>
     <row r="19">
@@ -5719,49 +5719,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C20" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D20" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E20" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F20" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G20" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H20" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I20" t="n">
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K20" t="n">
-        <v>575.7700000000002</v>
+        <v>598.13</v>
       </c>
       <c r="L20" t="n">
-        <v>1129.18</v>
+        <v>1151.54</v>
       </c>
       <c r="M20" t="n">
-        <v>1129.18</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N20" t="n">
-        <v>1682.59</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5785,10 +5785,10 @@
         <v>974.4145997704354</v>
       </c>
       <c r="X20" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y20" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="21">
@@ -5858,13 +5858,13 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V21" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W21" t="n">
-        <v>564.8317184882503</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X21" t="n">
-        <v>140.7279412706871</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y21" t="n">
         <v>90.8376455473191</v>
@@ -5956,22 +5956,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C23" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D23" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E23" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F23" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G23" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H23" t="n">
         <v>44.72</v>
@@ -5980,19 +5980,19 @@
         <v>44.72</v>
       </c>
       <c r="J23" t="n">
-        <v>179.7320762183977</v>
+        <v>44.72</v>
       </c>
       <c r="K23" t="n">
-        <v>179.7320762183977</v>
+        <v>598.13</v>
       </c>
       <c r="L23" t="n">
-        <v>179.7320762183977</v>
+        <v>598.13</v>
       </c>
       <c r="M23" t="n">
-        <v>690.5809049473327</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="N23" t="n">
-        <v>1243.990904947333</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="O23" t="n">
         <v>1797.400904947332</v>
@@ -6016,16 +6016,16 @@
         <v>1548.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W23" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X23" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y23" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>119.2429040110725</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C24" t="n">
-        <v>108.0308712378207</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D24" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E24" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F24" t="n">
         <v>44.72</v>
@@ -6101,10 +6101,10 @@
         <v>628.142589726071</v>
       </c>
       <c r="X24" t="n">
-        <v>204.0388125085078</v>
+        <v>483.794852723088</v>
       </c>
       <c r="Y24" t="n">
-        <v>154.1485167851398</v>
+        <v>433.9045569997199</v>
       </c>
     </row>
     <row r="25">
@@ -6217,25 +6217,25 @@
         <v>58.64</v>
       </c>
       <c r="J26" t="n">
-        <v>58.64</v>
+        <v>449.9491130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>768.3463663478684</v>
+        <v>1159.655479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1494.016366347868</v>
+        <v>1885.325479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>2004.865195076804</v>
+        <v>1885.325479385524</v>
       </c>
       <c r="N26" t="n">
-        <v>2618.085514851567</v>
+        <v>2498.545799160288</v>
       </c>
       <c r="O26" t="n">
-        <v>2932</v>
+        <v>2498.545799160288</v>
       </c>
       <c r="P26" t="n">
-        <v>2932</v>
+        <v>2498.545799160288</v>
       </c>
       <c r="Q26" t="n">
         <v>2932</v>
@@ -6296,16 +6296,16 @@
         <v>58.64</v>
       </c>
       <c r="J27" t="n">
-        <v>182.596520175299</v>
+        <v>430.5519615828727</v>
       </c>
       <c r="K27" t="n">
-        <v>371.7893362696824</v>
+        <v>619.744777677256</v>
       </c>
       <c r="L27" t="n">
-        <v>643.1397978648824</v>
+        <v>891.0952392724561</v>
       </c>
       <c r="M27" t="n">
-        <v>729.2203396077417</v>
+        <v>977.1757810153154</v>
       </c>
       <c r="N27" t="n">
         <v>1110.456065622884</v>
@@ -6381,19 +6381,19 @@
         <v>1182.871843630703</v>
       </c>
       <c r="L28" t="n">
-        <v>1182.871843630703</v>
+        <v>1060.096461653148</v>
       </c>
       <c r="M28" t="n">
-        <v>1182.871843630703</v>
+        <v>1060.096461653148</v>
       </c>
       <c r="N28" t="n">
-        <v>910.9677271946573</v>
+        <v>1060.096461653148</v>
       </c>
       <c r="O28" t="n">
-        <v>569.1035210542382</v>
+        <v>876.8723487974025</v>
       </c>
       <c r="P28" t="n">
-        <v>569.1035210542382</v>
+        <v>487.5310383647991</v>
       </c>
       <c r="Q28" t="n">
         <v>487.5310383647991</v>
@@ -6454,7 +6454,7 @@
         <v>58.64</v>
       </c>
       <c r="J29" t="n">
-        <v>449.9491130376557</v>
+        <v>58.64</v>
       </c>
       <c r="K29" t="n">
         <v>643.6617564436343</v>
@@ -6478,7 +6478,7 @@
         <v>2932</v>
       </c>
       <c r="R29" t="n">
-        <v>2932</v>
+        <v>2924.702432944026</v>
       </c>
       <c r="S29" t="n">
         <v>2729.90630385077</v>
@@ -6530,22 +6530,22 @@
         <v>58.64</v>
       </c>
       <c r="I30" t="n">
-        <v>142.664877967565</v>
+        <v>58.64</v>
       </c>
       <c r="J30" t="n">
-        <v>266.6213981428639</v>
+        <v>182.596520175299</v>
       </c>
       <c r="K30" t="n">
-        <v>455.8142142372473</v>
+        <v>619.744777677256</v>
       </c>
       <c r="L30" t="n">
-        <v>727.1646758324473</v>
+        <v>891.0952392724561</v>
       </c>
       <c r="M30" t="n">
-        <v>813.2452175753066</v>
+        <v>977.1757810153154</v>
       </c>
       <c r="N30" t="n">
-        <v>946.5255021828749</v>
+        <v>1110.456065622884</v>
       </c>
       <c r="O30" t="n">
         <v>1349.498517306602</v>
@@ -6621,22 +6621,22 @@
         <v>1182.871843630703</v>
       </c>
       <c r="M31" t="n">
-        <v>1101.299360941264</v>
+        <v>1182.871843630703</v>
       </c>
       <c r="N31" t="n">
-        <v>829.3952445052182</v>
+        <v>910.9677271946573</v>
       </c>
       <c r="O31" t="n">
-        <v>487.5310383647991</v>
+        <v>910.9677271946573</v>
       </c>
       <c r="P31" t="n">
-        <v>487.5310383647991</v>
+        <v>521.6264167620539</v>
       </c>
       <c r="Q31" t="n">
-        <v>487.5310383647991</v>
+        <v>521.6264167620539</v>
       </c>
       <c r="R31" t="n">
-        <v>58.64</v>
+        <v>119.6233128311671</v>
       </c>
       <c r="S31" t="n">
         <v>58.64</v>
@@ -6691,31 +6691,31 @@
         <v>58.64</v>
       </c>
       <c r="J32" t="n">
-        <v>58.64</v>
+        <v>444.804218824701</v>
       </c>
       <c r="K32" t="n">
-        <v>768.3463663478684</v>
+        <v>1154.510585172569</v>
       </c>
       <c r="L32" t="n">
-        <v>768.3463663478684</v>
+        <v>1154.510585172569</v>
       </c>
       <c r="M32" t="n">
-        <v>768.3463663478684</v>
+        <v>1154.510585172569</v>
       </c>
       <c r="N32" t="n">
-        <v>1381.566686122632</v>
+        <v>1767.730904947332</v>
       </c>
       <c r="O32" t="n">
-        <v>2107.236686122631</v>
+        <v>2493.400904947332</v>
       </c>
       <c r="P32" t="n">
-        <v>2832.906686122632</v>
+        <v>2493.400904947332</v>
       </c>
       <c r="Q32" t="n">
         <v>2932</v>
       </c>
       <c r="R32" t="n">
-        <v>2924.702432944026</v>
+        <v>2932</v>
       </c>
       <c r="S32" t="n">
         <v>2729.90630385077</v>
@@ -6855,22 +6855,22 @@
         <v>1182.871843630703</v>
       </c>
       <c r="L34" t="n">
-        <v>1060.096461653148</v>
+        <v>1182.871843630703</v>
       </c>
       <c r="M34" t="n">
-        <v>1060.096461653148</v>
+        <v>962.0318321129755</v>
       </c>
       <c r="N34" t="n">
-        <v>1060.096461653148</v>
+        <v>789.8455165730227</v>
       </c>
       <c r="O34" t="n">
-        <v>915.6515095017668</v>
+        <v>447.9813104326035</v>
       </c>
       <c r="P34" t="n">
-        <v>915.6515095017668</v>
+        <v>58.64</v>
       </c>
       <c r="Q34" t="n">
-        <v>487.5310383647991</v>
+        <v>58.64</v>
       </c>
       <c r="R34" t="n">
         <v>58.64</v>
@@ -6928,19 +6928,19 @@
         <v>44.72</v>
       </c>
       <c r="J35" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K35" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L35" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="M35" t="n">
-        <v>436.0291130376558</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="N35" t="n">
-        <v>690.5809049473327</v>
+        <v>1108.978828728935</v>
       </c>
       <c r="O35" t="n">
         <v>1243.990904947333</v>
@@ -6952,7 +6952,7 @@
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S35" t="n">
         <v>2085.68327354774</v>
@@ -7043,10 +7043,10 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V36" t="n">
-        <v>711.3477845844836</v>
+        <v>640.6349913485949</v>
       </c>
       <c r="W36" t="n">
-        <v>628.142589726071</v>
+        <v>557.4297964901822</v>
       </c>
       <c r="X36" t="n">
         <v>486.8613728079725</v>
@@ -7116,19 +7116,19 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U37" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V37" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W37" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X37" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y37" t="n">
         <v>807.7884919737335</v>
@@ -7159,25 +7159,25 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>137.1709049473328</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>690.5809049473327</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L38" t="n">
-        <v>1243.990904947333</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M38" t="n">
-        <v>1243.990904947333</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="N38" t="n">
-        <v>1243.990904947333</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="O38" t="n">
         <v>1797.400904947332</v>
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>55.93203277325181</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C39" t="n">
-        <v>44.72</v>
+        <v>108.0308712378206</v>
       </c>
       <c r="D39" t="n">
         <v>44.72</v>
@@ -7268,28 +7268,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R39" t="n">
-        <v>937.5750872192206</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S39" t="n">
-        <v>819.8336731135525</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>763.9167385504073</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U39" t="n">
-        <v>713.1992034391076</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V39" t="n">
-        <v>648.0369133466629</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W39" t="n">
-        <v>564.8317184882503</v>
+        <v>274.6072361907174</v>
       </c>
       <c r="X39" t="n">
-        <v>494.2632948060407</v>
+        <v>204.0388125085078</v>
       </c>
       <c r="Y39" t="n">
-        <v>444.3729990826727</v>
+        <v>154.1485167851397</v>
       </c>
     </row>
     <row r="40">
@@ -7353,13 +7353,13 @@
         <v>44.72</v>
       </c>
       <c r="T40" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U40" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V40" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
         <v>644.3484002705077</v>
@@ -7378,16 +7378,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
         <v>157.615990899539</v>
@@ -7405,22 +7405,22 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>690.5809049473327</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L41" t="n">
-        <v>1243.990904947333</v>
+        <v>1171.741171271065</v>
       </c>
       <c r="M41" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="N41" t="n">
-        <v>1243.990904947333</v>
+        <v>1682.59</v>
       </c>
       <c r="O41" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="P41" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q41" t="n">
         <v>2236</v>
@@ -7432,22 +7432,22 @@
         <v>2089.688719391593</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G42" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H42" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I42" t="n">
         <v>44.72</v>
@@ -7505,28 +7505,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>647.3506049216877</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S42" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T42" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U42" t="n">
-        <v>422.9747211415747</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V42" t="n">
-        <v>357.8124310491301</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W42" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X42" t="n">
-        <v>140.7279412706871</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.8376455473191</v>
+        <v>507.6838703204934</v>
       </c>
     </row>
     <row r="43">
@@ -7633,28 +7633,28 @@
         <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="K44" t="n">
-        <v>44.72</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="L44" t="n">
-        <v>44.72</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M44" t="n">
-        <v>555.568828728935</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N44" t="n">
-        <v>1108.978828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>1662.388828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P44" t="n">
         <v>1797.400904947332</v>
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>472.7782575464261</v>
+        <v>275.2516144816847</v>
       </c>
       <c r="C45" t="n">
-        <v>396.1722089875784</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D45" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F45" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G45" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H45" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I45" t="n">
         <v>44.72</v>
@@ -7754,16 +7754,16 @@
         <v>776.5100746769283</v>
       </c>
       <c r="V45" t="n">
-        <v>711.3477845844836</v>
+        <v>513.8211415197422</v>
       </c>
       <c r="W45" t="n">
-        <v>628.142589726071</v>
+        <v>430.6159466613296</v>
       </c>
       <c r="X45" t="n">
-        <v>557.5741660438614</v>
+        <v>360.0475229791199</v>
       </c>
       <c r="Y45" t="n">
-        <v>507.6838703204934</v>
+        <v>310.1572272557519</v>
       </c>
     </row>
     <row r="46">
@@ -7964,10 +7964,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>420.0430062450903</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>929.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>846.6934025142796</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O2" t="n">
         <v>455.2478695740924</v>
@@ -8204,16 +8204,16 @@
         <v>420.0430062450903</v>
       </c>
       <c r="K5" t="n">
-        <v>384.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>913.7065720867618</v>
+        <v>913.7065720867616</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
         <v>70.24786957409245</v>
@@ -8222,7 +8222,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.8226843274854</v>
+        <v>557.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8675,25 +8675,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>257.1230221309868</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O11" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>559.2870600406815</v>
+        <v>136.6628946047192</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>300.1141042229715</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -9152,25 +9152,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
         <v>629.2478695740924</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2870600406814136</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q17" t="n">
-        <v>313.9750954005603</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>141.1524110730753</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>544.2621276423173</v>
+        <v>637.6468801143703</v>
       </c>
       <c r="N20" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9623,10 +9623,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>171.4188408091284</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -9638,7 +9638,7 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>629.2478695740924</v>
+        <v>206.6237041381302</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
@@ -9860,7 +9860,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
         <v>716.8751175230994</v>
@@ -9869,19 +9869,19 @@
         <v>733</v>
       </c>
       <c r="M26" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N26" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>387.3332081078636</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>172.8226843274854</v>
+        <v>610.6552104282051</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,10 +10097,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>195.6693367737158</v>
+        <v>590.9310671147822</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10334,7 +10334,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>425.1078737447884</v>
       </c>
       <c r="K32" t="n">
         <v>716.8751175230994</v>
@@ -10352,10 +10352,10 @@
         <v>803.2478695740924</v>
       </c>
       <c r="P32" t="n">
-        <v>733.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q32" t="n">
-        <v>272.9169407692717</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10571,22 +10571,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>734.371980200822</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>629.2478695740924</v>
+        <v>206.6237041381304</v>
       </c>
       <c r="P35" t="n">
         <v>559.2870600406815</v>
@@ -10808,10 +10808,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>128.4277587171436</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
@@ -10820,10 +10820,10 @@
         <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>629.2478695740924</v>
+        <v>327.370891705079</v>
       </c>
       <c r="P38" t="n">
         <v>0.2870600406814136</v>
@@ -11048,25 +11048,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>257.1230221309868</v>
+        <v>184.14349316506</v>
       </c>
       <c r="L41" t="n">
         <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
         <v>477.2489580698352</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P41" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,13 +11282,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>171.4188408091283</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11297,10 +11297,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O44" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>136.6628946047192</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22703,7 +22703,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5911706460559</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.591170646055787</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -24596,22 +24596,22 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>121.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>218.6316114025499</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>269.1850752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>157.0536923518272</v>
       </c>
       <c r="P28" t="n">
-        <v>385.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>343.0825085630533</v>
+        <v>423.839266425598</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -24836,25 +24836,25 @@
         <v>121.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>137.8748535400052</v>
+        <v>218.6316114025499</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>338.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>385.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>423.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>26.61905508957324</v>
       </c>
       <c r="S31" t="n">
-        <v>60.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25070,25 +25070,25 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>121.5476281577792</v>
       </c>
       <c r="M34" t="n">
-        <v>218.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>269.1850752716849</v>
+        <v>98.72062288713161</v>
       </c>
       <c r="O34" t="n">
-        <v>195.4450614491477</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>385.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>423.839266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>424.6021279811511</v>
       </c>
       <c r="S34" t="n">
         <v>60.37347970285543</v>
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8834695.617792537</v>
+        <v>8834695.617792536</v>
       </c>
     </row>
     <row r="11">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13664553.4586438</v>
+        <v>13664553.45864379</v>
       </c>
     </row>
     <row r="16">
@@ -26278,7 +26278,7 @@
         <v>1227855.380931162</v>
       </c>
       <c r="E2" t="n">
-        <v>1227892.614324279</v>
+        <v>1227892.61432428</v>
       </c>
       <c r="F2" t="n">
         <v>1227892.61432428</v>
@@ -26290,7 +26290,7 @@
         <v>1227892.614324279</v>
       </c>
       <c r="I2" t="n">
-        <v>1227892.61432428</v>
+        <v>1227892.614324279</v>
       </c>
       <c r="J2" t="n">
         <v>1201472.069195665</v>
@@ -26305,7 +26305,7 @@
         <v>1227892.61432428</v>
       </c>
       <c r="N2" t="n">
-        <v>1227892.61432428</v>
+        <v>1227892.614324279</v>
       </c>
       <c r="O2" t="n">
         <v>1227892.61432428</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941388</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128454</v>
+        <v>540947.431225953</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>497080.9107622076</v>
+        <v>499048.754700107</v>
       </c>
       <c r="K4" t="n">
-        <v>495312.6122507454</v>
+        <v>497280.4561886448</v>
       </c>
       <c r="L4" t="n">
-        <v>493541.8013236982</v>
+        <v>495509.6452615976</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.485398499</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>464385.6560316529</v>
+        <v>462869.8003433371</v>
       </c>
       <c r="C6" t="n">
-        <v>601963.6361654667</v>
+        <v>600447.7804771512</v>
       </c>
       <c r="D6" t="n">
-        <v>604024.4080777828</v>
+        <v>602508.5523894673</v>
       </c>
       <c r="E6" t="n">
-        <v>280139.2110977442</v>
+        <v>278397.3612846372</v>
       </c>
       <c r="F6" t="n">
-        <v>623330.106443249</v>
+        <v>621588.2566301411</v>
       </c>
       <c r="G6" t="n">
-        <v>625275.6829114342</v>
+        <v>623533.8330983268</v>
       </c>
       <c r="H6" t="n">
-        <v>627223.9597287351</v>
+        <v>625482.1099156275</v>
       </c>
       <c r="I6" t="n">
-        <v>629174.9563720956</v>
+        <v>627433.1065589878</v>
       </c>
       <c r="J6" t="n">
-        <v>196067.9204334571</v>
+        <v>194100.0764955577</v>
       </c>
       <c r="K6" t="n">
-        <v>636204.2189449192</v>
+        <v>634236.3750070193</v>
       </c>
       <c r="L6" t="n">
-        <v>637975.0298719661</v>
+        <v>636007.1859340667</v>
       </c>
       <c r="M6" t="n">
-        <v>598606.5397821792</v>
+        <v>596864.6899690712</v>
       </c>
       <c r="N6" t="n">
-        <v>638971.4368170323</v>
+        <v>637229.5870039244</v>
       </c>
       <c r="O6" t="n">
-        <v>399339.1760747704</v>
+        <v>397597.3262616628</v>
       </c>
       <c r="P6" t="n">
-        <v>642909.7789257806</v>
+        <v>641167.9291126729</v>
       </c>
     </row>
   </sheetData>
@@ -26984,7 +26984,7 @@
         <v>350</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -26999,7 +26999,7 @@
         <v>302</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27039,13 +27039,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>-0</v>
@@ -27481,10 +27481,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>222.1724074428797</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27512,10 +27512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>42.5822945752962</v>
       </c>
       <c r="C3" t="n">
-        <v>19.1256503744886</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27600,22 +27600,22 @@
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>228.7711261016186</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>120.2890433732182</v>
+        <v>245.1446487409731</v>
       </c>
       <c r="K4" t="n">
         <v>288.520773801143</v>
@@ -27642,10 +27642,10 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>400</v>
+        <v>210.0245665062577</v>
       </c>
       <c r="U4" t="n">
         <v>400</v>
@@ -27685,7 +27685,7 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>400</v>
+        <v>371.2938086145855</v>
       </c>
       <c r="H5" t="n">
         <v>400</v>
@@ -27724,7 +27724,7 @@
         <v>400</v>
       </c>
       <c r="T5" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27755,16 +27755,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>165.0522469226136</v>
+        <v>148.1196855757283</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -27831,31 +27831,31 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>358.6673581080153</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>342.3286894602743</v>
       </c>
       <c r="H7" t="n">
+        <v>228.7711261016186</v>
+      </c>
+      <c r="I7" t="n">
         <v>400</v>
       </c>
-      <c r="I7" t="n">
-        <v>176.6334556201183</v>
-      </c>
       <c r="J7" t="n">
-        <v>35.26894883590776</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27885,19 +27885,19 @@
         <v>400</v>
       </c>
       <c r="U7" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>400</v>
       </c>
       <c r="Y7" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>47.84788425108593</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28031,19 +28031,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>306.7062506388764</v>
+        <v>400</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
       </c>
       <c r="T9" t="n">
-        <v>20.35776521751382</v>
+        <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>15.21035976018675</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
@@ -28074,19 +28074,19 @@
         <v>400</v>
       </c>
       <c r="E10" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F10" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G10" t="n">
+        <v>266.6880007226452</v>
+      </c>
+      <c r="H10" t="n">
+        <v>228.7711261016186</v>
+      </c>
+      <c r="I10" t="n">
         <v>400</v>
-      </c>
-      <c r="F10" t="n">
-        <v>400</v>
-      </c>
-      <c r="G10" t="n">
-        <v>400</v>
-      </c>
-      <c r="H10" t="n">
-        <v>400</v>
-      </c>
-      <c r="I10" t="n">
-        <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
         <v>35.26894883590776</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
         <v>210.0245665062577</v>
@@ -28125,7 +28125,7 @@
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>224.3505994565259</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
@@ -28134,7 +28134,7 @@
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28147,7 +28147,7 @@
         <v>350</v>
       </c>
       <c r="C11" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="D11" t="n">
         <v>350</v>
@@ -28201,7 +28201,7 @@
         <v>350</v>
       </c>
       <c r="U11" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="V11" t="n">
         <v>350</v>
@@ -28232,7 +28232,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>279.9943346964702</v>
       </c>
       <c r="F12" t="n">
         <v>339.6362423378769</v>
@@ -28271,7 +28271,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S12" t="n">
         <v>350</v>
@@ -28280,7 +28280,7 @@
         <v>350</v>
       </c>
       <c r="U12" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="V12" t="n">
         <v>350</v>
@@ -28292,7 +28292,7 @@
         <v>350</v>
       </c>
       <c r="Y12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -28393,7 +28393,7 @@
         <v>350</v>
       </c>
       <c r="F14" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="G14" t="n">
         <v>350</v>
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28463,7 +28463,7 @@
         <v>350</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D15" t="n">
         <v>347.9376868977026</v>
@@ -28472,7 +28472,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
-        <v>276.9584798124343</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
         <v>325.7395358750273</v>
@@ -28514,13 +28514,13 @@
         <v>350</v>
       </c>
       <c r="T15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>350</v>
       </c>
       <c r="V15" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="W15" t="n">
         <v>350</v>
@@ -28666,10 +28666,10 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S17" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T17" t="n">
         <v>350</v>
@@ -28712,7 +28712,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>325.7395358750273</v>
+        <v>86.14103844006453</v>
       </c>
       <c r="H18" t="n">
         <v>332.1680871864211</v>
@@ -28742,10 +28742,10 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="S18" t="n">
         <v>350</v>
@@ -28754,7 +28754,7 @@
         <v>350</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="V18" t="n">
         <v>350</v>
@@ -28876,7 +28876,7 @@
         <v>350</v>
       </c>
       <c r="I20" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28921,7 +28921,7 @@
         <v>350</v>
       </c>
       <c r="X20" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="Y20" t="n">
         <v>350</v>
@@ -28994,7 +28994,7 @@
         <v>350</v>
       </c>
       <c r="V21" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="W21" t="n">
         <v>350</v>
@@ -29003,7 +29003,7 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
     </row>
     <row r="22">
@@ -29110,7 +29110,7 @@
         <v>350</v>
       </c>
       <c r="H23" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I23" t="n">
         <v>150.0811596826846</v>
@@ -29152,7 +29152,7 @@
         <v>350</v>
       </c>
       <c r="V23" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="W23" t="n">
         <v>350</v>
@@ -29177,13 +29177,13 @@
         <v>350</v>
       </c>
       <c r="D24" t="n">
-        <v>285.2599243722602</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>325.7395358750273</v>
@@ -29237,7 +29237,7 @@
         <v>350</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>276.9584798124343</v>
       </c>
       <c r="Y24" t="n">
         <v>350</v>
@@ -29432,7 +29432,7 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>250.4600418258321</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -29444,7 +29444,7 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>250.460041825832</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -29614,10 +29614,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>250.8785988282945</v>
+        <v>243.6540074428798</v>
       </c>
       <c r="S29" t="n">
-        <v>294.7754086145854</v>
+        <v>302</v>
       </c>
       <c r="T29" t="n">
         <v>302</v>
@@ -29666,13 +29666,13 @@
         <v>302</v>
       </c>
       <c r="I30" t="n">
-        <v>302</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>250.460041825832</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -29684,7 +29684,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>165.5864277171805</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -29851,10 +29851,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>243.6540074428798</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
-        <v>302</v>
+        <v>294.7754086145854</v>
       </c>
       <c r="T32" t="n">
         <v>302</v>
@@ -30088,10 +30088,10 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S35" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T35" t="n">
         <v>350</v>
@@ -30179,13 +30179,13 @@
         <v>350</v>
       </c>
       <c r="V36" t="n">
-        <v>350</v>
+        <v>279.9943346964701</v>
       </c>
       <c r="W36" t="n">
         <v>350</v>
       </c>
       <c r="X36" t="n">
-        <v>279.99433469647</v>
+        <v>350</v>
       </c>
       <c r="Y36" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30267,7 +30267,7 @@
         <v>350</v>
       </c>
       <c r="Y37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="38">
@@ -30295,10 +30295,10 @@
         <v>350</v>
       </c>
       <c r="H38" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30356,13 +30356,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C39" t="n">
         <v>350</v>
       </c>
       <c r="D39" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722602</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -30404,7 +30404,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="S39" t="n">
         <v>350</v>
@@ -30419,7 +30419,7 @@
         <v>350</v>
       </c>
       <c r="W39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>350</v>
@@ -30489,7 +30489,7 @@
         <v>350</v>
       </c>
       <c r="T40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U40" t="n">
         <v>350</v>
@@ -30498,7 +30498,7 @@
         <v>350</v>
       </c>
       <c r="W40" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="X40" t="n">
         <v>350</v>
@@ -30526,7 +30526,7 @@
         <v>350</v>
       </c>
       <c r="F41" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G41" t="n">
         <v>350</v>
@@ -30568,7 +30568,7 @@
         <v>350</v>
       </c>
       <c r="T41" t="n">
-        <v>350</v>
+        <v>346.0346086145854</v>
       </c>
       <c r="U41" t="n">
         <v>350</v>
@@ -30602,7 +30602,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>147.1207205878186</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
@@ -30614,7 +30614,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I42" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30641,7 +30641,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30656,7 +30656,7 @@
         <v>350</v>
       </c>
       <c r="W42" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="X42" t="n">
         <v>350</v>
@@ -30769,10 +30769,10 @@
         <v>350</v>
       </c>
       <c r="H44" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30833,10 +30833,10 @@
         <v>350</v>
       </c>
       <c r="C45" t="n">
-        <v>285.2599243722601</v>
+        <v>350</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E45" t="n">
         <v>342.6720972219126</v>
@@ -30851,7 +30851,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30890,7 +30890,7 @@
         <v>350</v>
       </c>
       <c r="V45" t="n">
-        <v>350</v>
+        <v>154.448623365906</v>
       </c>
       <c r="W45" t="n">
         <v>350</v>
@@ -34743,10 +34743,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>369.4444444444445</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -34755,7 +34755,7 @@
         <v>385</v>
       </c>
       <c r="N2" t="n">
-        <v>369.4444444444443</v>
+        <v>385</v>
       </c>
       <c r="O2" t="n">
         <v>385</v>
@@ -34886,22 +34886,22 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
-        <v>85.02009453731046</v>
+        <v>209.8756999050654</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34928,10 +34928,10 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>249.0416087255421</v>
@@ -34983,17 +34983,17 @@
         <v>385</v>
       </c>
       <c r="K5" t="n">
-        <v>384.9999999999999</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>369.4444444444443</v>
+      </c>
+      <c r="N5" t="n">
         <v>385</v>
       </c>
-      <c r="M5" t="n">
-        <v>369.4444444444445</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
@@ -35001,7 +35001,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35117,31 +35117,31 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>84.28450214027332</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>97.28481661874426</v>
       </c>
       <c r="H7" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35171,19 +35171,19 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="8">
@@ -35360,19 +35360,19 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>154.95612715847</v>
+        <v>21.64412788111515</v>
       </c>
       <c r="H10" t="n">
-        <v>171.2288738983814</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35411,7 +35411,7 @@
         <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>25.18028924030974</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
@@ -35420,7 +35420,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35454,25 +35454,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L11" t="n">
-        <v>257.1230221309868</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>559</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>300.1141042229715</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35931,25 +35931,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>516.0089179080152</v>
+      </c>
+      <c r="N17" t="n">
         <v>559</v>
-      </c>
-      <c r="L17" t="n">
-        <v>559</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>559</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q17" t="n">
-        <v>141.1524110730749</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>141.1524110730753</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>559</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>93.38475247205298</v>
       </c>
       <c r="N20" t="n">
         <v>559</v>
       </c>
       <c r="O20" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36402,10 +36402,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>136.375834564038</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -36417,7 +36417,7 @@
         <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>559</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L26" t="n">
         <v>733</v>
       </c>
       <c r="M26" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>317.0853385337711</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>437.8325261007197</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36718,7 +36718,7 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>125.2086062376757</v>
+        <v>375.6686480635078</v>
       </c>
       <c r="K27" t="n">
         <v>191.1038546407913</v>
@@ -36730,7 +36730,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N27" t="n">
-        <v>385.0865919344868</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O27" t="n">
         <v>241.4570219027464</v>
@@ -36876,10 +36876,10 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>195.6693367737158</v>
+        <v>590.9310671147822</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -36952,13 +36952,13 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>84.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>191.1038546407913</v>
+        <v>441.5638964666233</v>
       </c>
       <c r="L30" t="n">
         <v>274.091375348687</v>
@@ -36970,7 +36970,7 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O30" t="n">
-        <v>407.0434496199268</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P30" t="n">
         <v>113.6660045146532</v>
@@ -37113,7 +37113,7 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>390.064867499698</v>
       </c>
       <c r="K32" t="n">
         <v>716.8751175230994</v>
@@ -37131,10 +37131,10 @@
         <v>733</v>
       </c>
       <c r="P32" t="n">
-        <v>733</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>100.0942564417863</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37350,22 +37350,22 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>257.1230221309867</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>559</v>
+        <v>136.375834564038</v>
       </c>
       <c r="P35" t="n">
         <v>559</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37553,7 +37553,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y37" t="n">
-        <v>54.74597778467183</v>
+        <v>62.53464715053764</v>
       </c>
     </row>
     <row r="38">
@@ -37587,10 +37587,10 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>93.38475247205329</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
@@ -37599,10 +37599,10 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>559</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37775,7 +37775,7 @@
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U40" t="n">
         <v>199.0416087255421</v>
@@ -37784,7 +37784,7 @@
         <v>150.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>123.6271901612903</v>
+        <v>115.8385207954244</v>
       </c>
       <c r="X40" t="n">
         <v>102.5563545698924</v>
@@ -37827,25 +37827,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>257.1230221309868</v>
+        <v>184.14349316506</v>
       </c>
       <c r="L41" t="n">
         <v>559</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -38061,13 +38061,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38076,10 +38076,10 @@
         <v>559</v>
       </c>
       <c r="O44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>136.3758345640378</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
